--- a/data/trans_orig/P36BPD01_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023</t>
+          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>619307</t>
+          <t>619059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>630981</t>
+          <t>630808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>652229</t>
+          <t>651629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>664737</t>
+          <t>664311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1275957</t>
+          <t>1276170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1293039</t>
+          <t>1292531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16134</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>18280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>34641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1094650</t>
+          <t>1098705</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1156329</t>
+          <t>1157599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>894466</t>
+          <t>896589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>919554</t>
+          <t>919432</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2007296</t>
+          <t>2004031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2070345</t>
+          <t>2068730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31137</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92816</t>
+          <t>88761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>36693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61659</t>
+          <t>59536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73246</t>
+          <t>74861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136295</t>
+          <t>139560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>609686</t>
+          <t>607478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>647379</t>
+          <t>645386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>839067</t>
+          <t>840465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>896889</t>
+          <t>898140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1465487</t>
+          <t>1466665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1542195</t>
+          <t>1542820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46298</t>
+          <t>48291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83991</t>
+          <t>86199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33729</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91551</t>
+          <t>90153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>82099</t>
+          <t>81474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158807</t>
+          <t>157629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>876010</t>
+          <t>876321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>904448</t>
+          <t>903671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1043124</t>
+          <t>1045416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1069226</t>
+          <t>1069897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1929408</t>
+          <t>1930836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1967676</t>
+          <t>1968208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49113</t>
+          <t>48802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50182</t>
+          <t>47890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50753</t>
+          <t>50221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89021</t>
+          <t>87593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3242677</t>
+          <t>3239663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3318017</t>
+          <t>3314832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3468372</t>
+          <t>3467078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3524900</t>
+          <t>3528030</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6728011</t>
+          <t>6725947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6820115</t>
+          <t>6823898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123690</t>
+          <t>126875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199030</t>
+          <t>202044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130519</t>
+          <t>127389</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187047</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>277011</t>
+          <t>273228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369115</t>
+          <t>371179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD01_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>626659</t>
+          <t>677132</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>619059</t>
+          <t>666317</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>630808</t>
+          <t>683595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>658936</t>
+          <t>712658</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>651629</t>
+          <t>704022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>664311</t>
+          <t>718656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1285595</t>
+          <t>1389790</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1276170</t>
+          <t>1377886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1292531</t>
+          <t>1398946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>13578</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34641</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1125749</t>
+          <t>963782</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1098705</t>
+          <t>940178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1157599</t>
+          <t>982856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>909731</t>
+          <t>1015987</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>896589</t>
+          <t>1003207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>919432</t>
+          <t>1026464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2035480</t>
+          <t>1979769</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2004031</t>
+          <t>1954115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2068730</t>
+          <t>2001553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>61717</t>
+          <t>79903</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88761</t>
+          <t>103507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>46394</t>
+          <t>51986</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>64766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>108111</t>
+          <t>131889</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74861</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139560</t>
+          <t>157543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1187466</t>
+          <t>1043685</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1187466</t>
+          <t>1043685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1187466</t>
+          <t>1043685</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956125</t>
+          <t>1067973</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956125</t>
+          <t>1067973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956125</t>
+          <t>1067973</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2143591</t>
+          <t>2111658</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2143591</t>
+          <t>2111658</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2143591</t>
+          <t>2111658</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>630731</t>
+          <t>715525</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>607478</t>
+          <t>692015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>645386</t>
+          <t>732482</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>865996</t>
+          <t>724886</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>840465</t>
+          <t>705101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>898140</t>
+          <t>741031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1496726</t>
+          <t>1440411</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1466665</t>
+          <t>1415227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1542820</t>
+          <t>1466231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62946</t>
+          <t>77228</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48291</t>
+          <t>60271</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>100738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64622</t>
+          <t>84471</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32478</t>
+          <t>68326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90153</t>
+          <t>104256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>127568</t>
+          <t>161699</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81474</t>
+          <t>135879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157629</t>
+          <t>186883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>693677</t>
+          <t>792753</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>693677</t>
+          <t>792753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>693677</t>
+          <t>792753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>930618</t>
+          <t>809357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>930618</t>
+          <t>809357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>930618</t>
+          <t>809357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1624294</t>
+          <t>1602110</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1624294</t>
+          <t>1602110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1624294</t>
+          <t>1602110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>893307</t>
+          <t>942177</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>876321</t>
+          <t>923905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>903671</t>
+          <t>955266</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1059089</t>
+          <t>1070650</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1045416</t>
+          <t>1055029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1069897</t>
+          <t>1082978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1952396</t>
+          <t>2012827</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1930836</t>
+          <t>1989216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1968208</t>
+          <t>2031042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>46163</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>33074</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48802</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34217</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23409</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47890</t>
+          <t>62271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>66033</t>
+          <t>92813</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50221</t>
+          <t>74598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87593</t>
+          <t>116424</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925123</t>
+          <t>988340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925123</t>
+          <t>988340</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925123</t>
+          <t>988340</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093306</t>
+          <t>1117300</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093306</t>
+          <t>1117300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093306</t>
+          <t>1117300</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018429</t>
+          <t>2105640</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018429</t>
+          <t>2105640</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018429</t>
+          <t>2105640</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3276446</t>
+          <t>3298616</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3239663</t>
+          <t>3260980</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3314832</t>
+          <t>3328952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3493752</t>
+          <t>3524181</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3467078</t>
+          <t>3495998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3528030</t>
+          <t>3551130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6770198</t>
+          <t>6822797</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6725947</t>
+          <t>6771769</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6823898</t>
+          <t>6861831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165261</t>
+          <t>216872</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126875</t>
+          <t>186536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202044</t>
+          <t>254508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>161667</t>
+          <t>203171</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127389</t>
+          <t>176222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>231354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>326928</t>
+          <t>420043</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273228</t>
+          <t>381009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>371179</t>
+          <t>471071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
